--- a/stories/arbres/ATOM-REL.MOQ.002-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hubert joue au bac à sable. Maman est sur le banc. Lila est à l'écart. Elle tient un seau. Elle ne parle pas. Hubert va la rejoindre. Il s'assoit près d'elle. Hubert dit : tu veux jouer ? Il invite Lila. Lila hoche la tête. Ils remplissent le seau. Le sable est froid. Maman sourit. Un peu plus tard, Lila reste encore à l'écart. Hubert la rejoint. Il l'invite encore. Si ça continue, on prévient un adulte. Hubert va vers maman. Il dit : Lila est encore à l'écart. Maman, l'adulte, vient. Elle s'assoit près d'elles. Hubert invite Lila au seau. Ils jouent. On rejoint. On invite. Un adulte si ça continue.</t>
+          <t>Hubert joue au bac à sable. Maman est sur le banc. Lila est à l'écart. Elle tient un seau. Elle ne parle pas. Hubert va la rejoindre. Il s'assoit près d'elle. Tu veux jouer ? Il invite Lila. Lila hoche la tête. Ils remplissent le seau. Le sable est froid. Maman sourit. Un peu plus tard, Lila reste encore à l'écart. Hubert la rejoint. Il l'invite encore. Si ça continue, on prévient un adulte. Hubert va vers maman. Lila est encore à l'écart. Maman, l'adulte, vient. Elle s'assoit près d'elles. Hubert invite Lila au seau. Ils jouent. On rejoint. On invite. Un adulte si ça continue.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hubert joue au bac à sable. Maman est sur le banc. Lila est à l'écart. Elle tient un seau. Elle ne parle pas. Hubert va la rejoindre. Il s'assoit près d'elle.
+enfant-m|Tu veux jouer ? Il invite Lila.
+narrateur|Lila hoche la tête. Ils remplissent le seau. Le sable est froid. Maman sourit. Un peu plus tard, Lila reste encore à l'écart. Hubert la rejoint. Il l'invite encore. Si ça continue, on prévient un adulte. Hubert va vers maman.
+narrateur|Lila est encore à l'écart. Maman, l'adulte, vient.
+narrateur|Elle s'assoit près d'elles. Hubert invite Lila au seau. Ils jouent. On rejoint. On invite. Un adulte si ça continue.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Lila est à l'écart. Que fait Hubert ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hubert a rejoint Lila. Il l'a invitée. Maman, l'adulte, a été prévenue.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Lila verse le sable. Hubert tient le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.002-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Elle s'assoit près d'elles. Hubert invite Lila au seau. Ils jouent. On rejoint. On invite. Un adulte si ça continue.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Lila est à l'écart. Que fait Hubert ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Hubert a rejoint Lila. Il l'a invitée. Maman, l'adulte, a été prévenue.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Lila verse le sable. Hubert tient le seau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.002-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hubert rejoint Lila à l'écart</t>
+          <t>Chouchou rejoint Mila au bac à sable</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +831,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le banc du bac a la peinture écaillée. Un pigeon picore. Chouchou voit Mila à l'écart avec un seau. Il la rejoint, l'invite. Ça continue. Il prévient maman. Ils remplissent le seau.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hubert joue au bac à sable. Maman est sur le banc. Lila est à l'écart. Elle tient un seau. Elle ne parle pas. Hubert va la rejoindre. Il s'assoit près d'elle. Tu veux jouer ? Il invite Lila. Lila hoche la tête. Ils remplissent le seau. Le sable est froid. Maman sourit. Un peu plus tard, Lila reste encore à l'écart. Hubert la rejoint. Il l'invite encore. Si ça continue, on prévient un adulte. Hubert va vers maman. Lila est encore à l'écart. Maman, l'adulte, vient. Elle s'assoit près d'elles. Hubert invite Lila au seau. Ils jouent. On rejoint. On invite. Un adulte si ça continue.</t>
+          <t>Le banc du bac a la peinture verte écaillée. Un petit morceau de peinture lève, tout sec. Un pigeon picore, puis s'envole. Ses ailes font un bruit court. Le seau vert est froid, un peu rêche. Le panier de maman sent le pain. Je m'assieds ici, Chouchou. Le bois est tiède, tu sens ? Oui, maman. Tu vas au bac ? Oui. En ce moment, Chouchou est au bac à sable. Le sable est froid, sous les doigts. Il coule, tout fin. Mila est à l'écart. Elle tient un seau. Elle ne parle pas. Ses épaules sont basses. Tu peux la rejoindre. Rejoindre, c'est aller vers elle. Chouchou va la rejoindre. Il s'assoit près d'elle. Le sable gratte un peu, sur les genoux. Tu veux jouer ? Inviter, c'est demander. Mila hoche la tête. Ils remplissent le seau. Le sable est froid. Il sonne, tout doux, dans le plastique. Vous tenez bien le seau. Bravo. Un peu plus tard, Mila reste encore à l'écart. Chouchou la rejoint. Il l'invite encore. Tu veux le seau, avec moi ? Mila s'approche. Ça continue un peu, plus loin. Si ça continue, on prévient un adulte. Chouchou va vers maman. Mila est encore à l'écart. Ça continue. Je t'écoute, Chouchou. Je viens. Maman, l'adulte, vient. Elle s'assoit près d'eux. On reste ici, tous les trois. On rejoint. On invite. Oui. Un adulte, si ça continue. Chouchou invite Mila au seau. Ils jouent. Le seau se remplit, puis se vide. Bravo, Chouchou. Tu as rejoint Mila. Tu l'as invitée. Tu m'as prévenue. C'est du bon travail. Vous avez fini de remplir le seau ? Encore un peu. D'accord. Le sable est froid, on le sent bien. Un grain de sable reste sous un ongle. Tu le sors tout doux ? Oui. L'anse du seau est rêche, un peu. Une petite pelle attend, à côté. La pelle, on la laisse au bac. D'accord. Le pigeon est parti. Une plume grise reste sur le sable. La peinture écaillée reste sur le banc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1325,85 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hubert joue au bac à sable. Maman est sur le banc. Lila est à l'écart. Elle tient un seau. Elle ne parle pas. Hubert va la rejoindre. Il s'assoit près d'elle.
-enfant-m|Tu veux jouer ? Il invite Lila.
-narrateur|Lila hoche la tête. Ils remplissent le seau. Le sable est froid. Maman sourit. Un peu plus tard, Lila reste encore à l'écart. Hubert la rejoint. Il l'invite encore. Si ça continue, on prévient un adulte. Hubert va vers maman.
-narrateur|Lila est encore à l'écart. Maman, l'adulte, vient.
-narrateur|Elle s'assoit près d'elles. Hubert invite Lila au seau. Ils jouent. On rejoint. On invite. Un adulte si ça continue.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le banc du bac a la peinture verte écaillée.
+narrateur|Un petit morceau de peinture lève, tout sec.
+narrateur|Un pigeon picore, puis s'envole.
+narrateur|Ses ailes font un bruit court.
+narrateur|Le seau vert est froid, un peu rêche.
+narrateur|Le panier de maman sent le pain.
+maman|Je m'assieds ici, Chouchou.
+maman|Le bois est tiède, tu sens ?
+enfant-m|Oui, maman.
+maman|Tu vas au bac ?
+enfant-m|Oui.
+narrateur|En ce moment, Chouchou est au bac à sable.
+narrateur|Le sable est froid, sous les doigts.
+narrateur|Il coule, tout fin.
+narrateur|Mila est à l'écart.
+narrateur|Elle tient un seau.
+narrateur|Elle ne parle pas.
+narrateur|Ses épaules sont basses.
+maman|Tu peux la rejoindre.
+maman|Rejoindre, c'est aller vers elle.
+narrateur|Chouchou va la rejoindre.
+narrateur|Il s'assoit près d'elle.
+narrateur|Le sable gratte un peu, sur les genoux.
+enfant-m|Tu veux jouer ?
+narrateur|Inviter, c'est demander.
+narrateur|Mila hoche la tête.
+narrateur|Ils remplissent le seau.
+narrateur|Le sable est froid.
+narrateur|Il sonne, tout doux, dans le plastique.
+maman|Vous tenez bien le seau.
+maman|Bravo.
+narrateur|Un peu plus tard, Mila reste encore à l'écart.
+narrateur|Chouchou la rejoint.
+narrateur|Il l'invite encore.
+enfant-m|Tu veux le seau, avec moi ?
+narrateur|Mila s'approche.
+narrateur|Ça continue un peu, plus loin.
+narrateur|Si ça continue, on prévient un adulte.
+narrateur|Chouchou va vers maman.
+enfant-m|Mila est encore à l'écart.
+enfant-m|Ça continue.
+maman|Je t'écoute, Chouchou.
+maman|Je viens.
+narrateur|Maman, l'adulte, vient.
+narrateur|Elle s'assoit près d'eux.
+maman|On reste ici, tous les trois.
+enfant-m|On rejoint.
+enfant-m|On invite.
+maman|Oui.
+maman|Un adulte, si ça continue.
+narrateur|Chouchou invite Mila au seau.
+narrateur|Ils jouent.
+narrateur|Le seau se remplit, puis se vide.
+maman|Bravo, Chouchou.
+maman|Tu as rejoint Mila.
+maman|Tu l'as invitée.
+maman|Tu m'as prévenue.
+maman|C'est du bon travail.
+maman|Vous avez fini de remplir le seau ?
+enfant-m|Encore un peu.
+maman|D'accord.
+maman|Le sable est froid, on le sent bien.
+narrateur|Un grain de sable reste sous un ongle.
+maman|Tu le sors tout doux ?
+enfant-m|Oui.
+narrateur|L'anse du seau est rêche, un peu.
+narrateur|Une petite pelle attend, à côté.
+maman|La pelle, on la laisse au bac.
+enfant-m|D'accord.
+narrateur|Le pigeon est parti.
+narrateur|Une plume grise reste sur le sable.
+narrateur|La peinture écaillée reste sur le banc.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1428,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lila est à l'écart. Que fait Hubert ?</t>
+          <t>Mila est à l'écart. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1584,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Lila est à l'écart. Que fait Hubert ?</t>
+          <t>narrateur|Mila est à l'écart.
+narrateur|Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1613,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hubert a rejoint Lila. Il l'a invitée. Maman, l'adulte, a été prévenue.</t>
+          <t>Chouchou a rejoint Mila. Il l'a invitée. Maman, l'adulte, a été prévenue. Bravo, Chouchou. Tu as fait du bon travail. J'ai rejoint. J'ai invité. Oui. Et tu m'as prévenue.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1757,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hubert a rejoint Lila. Il l'a invitée. Maman, l'adulte, a été prévenue.</t>
+          <t>narrateur|Chouchou a rejoint Mila.
+narrateur|Il l'a invitée.
+narrateur|Maman, l'adulte, a été prévenue.
+maman|Bravo, Chouchou.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai rejoint.
+enfant-m|J'ai invité.
+maman|Oui.
+maman|Et tu m'as prévenue.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Lila verse le sable. Hubert tient le seau.</t>
+          <t>Mila verse le sable. Chouchou tient le seau. Il est lourd, maintenant ? Oui, maman. On le pose près du banc ? Oui. Le seau sonne, sur le bois écaillé. Le pigeon peut revenir, plus tard. Le pain du panier sent encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,7 +1929,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Lila verse le sable. Hubert tient le seau.</t>
+          <t>narrateur|Mila verse le sable.
+narrateur|Chouchou tient le seau.
+maman|Il est lourd, maintenant ?
+enfant-m|Oui, maman.
+maman|On le pose près du banc ?
+enfant-m|Oui.
+narrateur|Le seau sonne, sur le bois écaillé.
+maman|Le pigeon peut revenir, plus tard.
+narrateur|Le pain du panier sent encore.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1864,7 +1965,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué avec le seau. Bravo. Tu as rejoint Mila. Tu as fait du bon travail. La peinture verte reste écaillée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,7 +2105,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué avec le seau.
+maman|Bravo.
+maman|Tu as rejoint Mila.
+maman|Tu as fait du bon travail.
+narrateur|La peinture verte reste écaillée.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2026,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.002-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-06.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le banc du bac a la peinture verte écaillée. Un petit morceau de peinture lève, tout sec. Un pigeon picore, puis s'envole. Ses ailes font un bruit court. Le seau vert est froid, un peu rêche. Le panier de maman sent le pain. Je m'assieds ici, Chouchou. Le bois est tiède, tu sens ? Oui, maman. Tu vas au bac ? Oui. En ce moment, Chouchou est au bac à sable. Le sable est froid, sous les doigts. Il coule, tout fin. Mila est à l'écart. Elle tient un seau. Elle ne parle pas. Ses épaules sont basses. Tu peux la rejoindre. Rejoindre, c'est aller vers elle. Chouchou va la rejoindre. Il s'assoit près d'elle. Le sable gratte un peu, sur les genoux. Tu veux jouer ? Inviter, c'est demander. Mila hoche la tête. Ils remplissent le seau. Le sable est froid. Il sonne, tout doux, dans le plastique. Vous tenez bien le seau. Bravo. Un peu plus tard, Mila reste encore à l'écart. Chouchou la rejoint. Il l'invite encore. Tu veux le seau, avec moi ? Mila s'approche. Ça continue un peu, plus loin. Si ça continue, on prévient un adulte. Chouchou va vers maman. Mila est encore à l'écart. Ça continue. Je t'écoute, Chouchou. Je viens. Maman, l'adulte, vient. Elle s'assoit près d'eux. On reste ici, tous les trois. On rejoint. On invite. Oui. Un adulte, si ça continue. Chouchou invite Mila au seau. Ils jouent. Le seau se remplit, puis se vide. Bravo, Chouchou. Tu as rejoint Mila. Tu l'as invitée. Tu m'as prévenue. C'est du bon travail. Vous avez fini de remplir le seau ? Encore un peu. D'accord. Le sable est froid, on le sent bien. Un grain de sable reste sous un ongle. Tu le sors tout doux ? Oui. L'anse du seau est rêche, un peu. Une petite pelle attend, à côté. La pelle, on la laisse au bac. D'accord. Le pigeon est parti. Une plume grise reste sur le sable. La peinture écaillée reste sur le banc.</t>
+          <t>Le banc du bac a la peinture verte écaillée. Un petit morceau de peinture lève, tout sec. Un pigeon picore, puis s'envole. Ses ailes font un bruit court. Le seau vert est froid, un peu rêche. Le panier de maman sent le pain. Je m'assieds ici, Chouchou. Le bois est tiède, tu sens ? Oui, maman. Tu vas au bac ? Oui. En ce moment, Chouchou est au bac à sable. Le sable est froid, sous les doigts. Il coule, tout fin. Mila est à l'écart. Elle tient un seau. Elle ne parle pas. Ses épaules sont basses. Tu peux la rejoindre. Rejoindre, c'est aller vers elle. Chouchou va la rejoindre. Il s'assoit près d'elle. Le sable gratte un peu, sur les genoux. Tu veux jouer ? Inviter, c'est demander. Mila hoche la tête. Ils remplissent le seau. Le sable est froid. Il sonne, tout doux, dans le plastique. Vous tenez bien le seau. Bravo. Un peu plus tard, Mila reste encore à l'écart. Chouchou la rejoint. Il l'invite encore. Tu veux le seau, avec moi ? Mila s'approche. Ça continue un peu, plus loin. Si ça continue, on prévient un adulte. Chouchou va vers maman. Mila est encore à l'écart. Ça continue. Je t'écoute, Chouchou. Je viens. Maman, l'adulte, vient. Elle s'assoit près d'eux. On reste ici, tous les trois. On rejoint. On invite. Oui. Un adulte, si ça continue. Chouchou invite Mila au seau. Ils jouent. Le seau se remplit, puis se vide. Bravo, Chouchou. Tu as rejoint Mila. Tu l'as invitée. Tu m'as prévenue. Vous avez fini de remplir le seau ? Encore un peu. D'accord. Le sable est froid, on le sent bien. Un grain de sable reste sous un ongle. Tu le sors tout doux ? Oui. L'anse du seau est rêche, un peu. Une petite pelle attend, à côté. La pelle, on la laisse au bac. D'accord. Le pigeon est parti. Une plume grise reste sur le sable. La peinture écaillée reste sur le banc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hubert joue au bac à sable. Maman est sur le banc. Lila est à l'écart. Elle tient un seau. Elle ne parle pas. Hubert va la &lt;emphasis level="moderate"&gt;rejoindre&lt;/emphasis&gt;. Il s'assoit près d'elle. Hubert dit : tu veux jouer ? Il invite Lila. Lila hoche la tête. Ils remplissent le seau. Le sable est froid. Maman sourit. Un peu plus tard, Lila reste encore à l'écart. Hubert la rejoint. Il l'invite encore. Si ça continue, on prévient un adulte. Hubert va vers maman. Il dit : Lila est encore à l'écart. Maman, l'adulte, vient. Elle s'assoit près d'elles. Hubert invite Lila au seau. Ils jouent. On rejoint. On invite. Un adulte si ça continue.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le banc du bac a la peinture verte écaillée. Un petit morceau de peinture lève, tout sec. Un pigeon picore, puis s'envole. Ses ailes font un bruit court. Le seau vert est froid, un peu rêche. Le panier de maman sent le pain. Je m'assieds ici, Chouchou. Le bois est tiède, tu sens ? Oui, maman. Tu vas au bac ? Oui. En ce moment, Chouchou est au bac à sable. Le sable est froid, sous les doigts. Il coule, tout fin. Mila est à l'écart. Elle tient un seau. Elle ne parle pas. Ses épaules sont basses. Tu peux la rejoindre. Rejoindre, c'est aller vers elle. Chouchou va la rejoindre. Il s'assoit près d'elle. Le sable gratte un peu, sur les genoux. Tu veux jouer ? Inviter, c'est demander. Mila hoche la tête. Ils remplissent le seau. Le sable est froid. Il sonne, tout doux, dans le plastique. Vous tenez bien le seau. Bravo. Un peu plus tard, Mila reste encore à l'écart. Chouchou la rejoint. Il l'invite encore. Tu veux le seau, avec moi ? Mila s'approche. Ça continue un peu, plus loin. Si ça continue, on prévient un adulte. Chouchou va vers maman. Mila est encore à l'écart. Ça continue. Je t'écoute, Chouchou. Je viens. Maman, l'adulte, vient. Elle s'assoit près d'eux. On reste ici, tous les trois. On rejoint. On invite. Oui. Un adulte, si ça continue. Chouchou invite Mila au seau. Ils jouent. Le seau se remplit, puis se vide. Bravo, Chouchou. Tu as rejoint Mila. Tu l'as invitée. Tu m'as prévenue. Vous avez fini de remplir le seau ? Encore un peu. D'accord. Le sable est froid, on le sent bien. Un grain de sable reste sous un ongle. Tu le sors tout doux ? Oui. L'anse du seau est rêche, un peu. Une petite pelle attend, à côté. La pelle, on la laisse au bac. D'accord. Le pigeon est parti. Une plume grise reste sur le sable. La peinture écaillée reste sur le banc.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1382,7 +1382,6 @@
 maman|Tu as rejoint Mila.
 maman|Tu l'as invitée.
 maman|Tu m'as prévenue.
-maman|C'est du bon travail.
 maman|Vous avez fini de remplir le seau ?
 enfant-m|Encore un peu.
 maman|D'accord.
@@ -1433,7 +1432,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Lila est à l'écart. Que fait Hubert ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila est à l'écart. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1588,7 +1587,6 @@
 narrateur|Que fait Chouchou ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1613,12 +1611,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a rejoint Mila. Il l'a invitée. Maman, l'adulte, a été prévenue. Bravo, Chouchou. Tu as fait du bon travail. J'ai rejoint. J'ai invité. Oui. Et tu m'as prévenue.</t>
+          <t>Chouchou a rejoint Mila. Il l'a invitée. Maman, l'adulte, a été prévenue. Bravo, Chouchou. J'ai rejoint. J'ai invité. Oui. Et tu m'as prévenue.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hubert a rejoint Lila. Il l'a invitée. Maman, l'&lt;emphasis level="moderate"&gt;adulte&lt;/emphasis&gt;, a été prévenue.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a rejoint Mila. Il l'a invitée. Maman, l'adulte, a été prévenue. Bravo, Chouchou. J'ai rejoint. J'ai invité. Oui. Et tu m'as prévenue.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1761,14 +1759,12 @@
 narrateur|Il l'a invitée.
 narrateur|Maman, l'adulte, a été prévenue.
 maman|Bravo, Chouchou.
-maman|Tu as fait du bon travail.
 enfant-m|J'ai rejoint.
 enfant-m|J'ai invité.
 maman|Oui.
 maman|Et tu m'as prévenue.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1798,7 +1794,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lila verse le sable. Hubert tient le seau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila verse le sable. Chouchou tient le seau. Il est lourd, maintenant ? Oui, maman. On le pose près du banc ? Oui. Le seau sonne, sur le bois écaillé. Le pigeon peut revenir, plus tard. Le pain du panier sent encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1940,7 +1936,6 @@
 narrateur|Le pain du panier sent encore.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a joué avec le seau. Bravo. Tu as rejoint Mila. Tu as fait du bon travail. La peinture verte reste écaillée. L'histoire est finie.</t>
+          <t>On a joué avec le seau. Bravo. Tu as rejoint Mila. La peinture verte reste écaillée.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a joué avec le seau. Bravo. Tu as rejoint Mila. La peinture verte reste écaillée.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2108,12 +2103,9 @@
           <t>enfant-m|On a joué avec le seau.
 maman|Bravo.
 maman|Tu as rejoint Mila.
-maman|Tu as fait du bon travail.
-narrateur|La peinture verte reste écaillée.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La peinture verte reste écaillée.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2132,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.002-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-06.xlsx
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hubert, Lila, maman</t>
+          <t>Chouchou, Mila, maman</t>
         </is>
       </c>
     </row>
